--- a/artfynd/A 6347-2026 artfynd.xlsx
+++ b/artfynd/A 6347-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136984104</v>
       </c>
       <c r="B2" t="n">
-        <v>30306</v>
+        <v>30319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6347-2026 artfynd.xlsx
+++ b/artfynd/A 6347-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136984104</v>
       </c>
       <c r="B2" t="n">
-        <v>30319</v>
+        <v>30321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6347-2026 artfynd.xlsx
+++ b/artfynd/A 6347-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136984104</v>
       </c>
       <c r="B2" t="n">
-        <v>30321</v>
+        <v>30331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6347-2026 artfynd.xlsx
+++ b/artfynd/A 6347-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136984104</v>
       </c>
       <c r="B2" t="n">
-        <v>30331</v>
+        <v>30332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
